--- a/feedback_forms/002_pre_experience_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/002_pre_experience_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>participant_background</t>
+          <t>participant_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>participant_background</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>participant_expectations</t>
+          <t>participant_how_heard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>participant_expectations</t>
+          <t>How did you hear about this event?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,15 +566,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>participant_background_questions</t>
+          <t>participant_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>participant_background_questions</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate this event?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rate from 1 to 5</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_previous_experience</t>
+          <t>participant_favorite_part</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>participant_previous_experience</t>
+          <t>What was your favorite part of the event?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,17 +616,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>participant_previous_experience_other</t>
+          <t>participant_event_rating</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>participant_previous_experience_other</t>
+          <t>How would you rate the event organization?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>If participant has not had an experience like this one before, please describe</t>
+          <t>Rate from 1 to 5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -639,12 +643,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>participant_previous_experience_other</t>
+          <t>participant_background</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant_previous_experience_other</t>
+          <t>What is your background in relation to this field/event?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +661,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>participant_expectations</t>
+          <t>participant_experience_length</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>participant_expectations</t>
+          <t>How long have you been working/practicing in this field?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,19 +689,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>participant_expectations_other</t>
+          <t>participant_motive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>participant_expectations_other</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>If participant has not had any prior experience, please describe</t>
-        </is>
-      </c>
+          <t>What motivated you to participate in this event?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -707,17 +707,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_organizer_background</t>
+          <t>participant_experience</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>event_organizer_background</t>
+          <t>Do you have any experience in events similar to this one?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -735,12 +735,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_organizer_name</t>
+          <t>participant_experience_other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>event_organizer_name</t>
+          <t>If you don't have experience in events similar to this one, can you describe your experience?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,17 +753,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>participant_background_questions_2</t>
+          <t>participant_expectations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_background_questions_2</t>
+          <t>What were your expectations for this event?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>participant_background_questions_3</t>
+          <t>participant_expectations_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>participant_background_questions_3</t>
+          <t>If you don't have any expectations, please describe why?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -804,12 +804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>participant_background_questions_4</t>
+          <t>participant_expectations_met</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>participant_background_questions_4</t>
+          <t>How were your expectations met?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -827,12 +827,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>participant_background_questions_5</t>
+          <t>participant_suggestion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>participant_background_questions_5</t>
+          <t>Do you have any suggestions for improvement?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -850,12 +850,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>participant_background_questions_6</t>
+          <t>event_organizer_background</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>participant_background_questions_6</t>
+          <t>What was your background in relation to the event organization?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -873,223 +873,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>participant_background_questions_7</t>
+          <t>participant_additional_info</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>participant_background_questions_7</t>
+          <t>Is there anything you'd like to add or comment about your experience?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>participant_background_questions_8</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>participant_background_questions_8</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>participant_background_questions_9</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>participant_background_questions_9</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>participant_background_questions_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>participant_background_questions_10</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>participant_background_questions_11</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>participant_background_questions_11</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>participant_background_questions_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>participant_background_questions_11</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>participant_background_questions_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>participant_background_questions_12</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>participant_background_questions_13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>participant_background_questions_13</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>participant_background_questions_14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>participant_background_questions_14</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>participant_background_questions_15</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>participant_background_questions_15</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1109,7 +902,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1134,7 +927,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>participant_previous_experience_choices</t>
+          <t>participant_experience_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1151,7 +944,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>participant_previous_experience_choices</t>
+          <t>participant_experience_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
